--- a/Result/profitability/1580.xlsx
+++ b/Result/profitability/1580.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.41</v>
       </c>
       <c r="M2" t="n">
-        <v>2.83</v>
+        <v>2.635</v>
       </c>
       <c r="N2" t="n">
-        <v>41.5175</v>
+        <v>41.245</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.63</v>
       </c>
       <c r="M3" t="n">
-        <v>2.4775</v>
+        <v>2.2725</v>
       </c>
       <c r="N3" t="n">
-        <v>40.66625000000001</v>
+        <v>40.31625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>2.21375</v>
+        <v>2.1125</v>
       </c>
       <c r="N4" t="n">
-        <v>39.27875</v>
+        <v>38.73125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.45</v>
       </c>
       <c r="M5" t="n">
-        <v>2.0575</v>
+        <v>1.92</v>
       </c>
       <c r="N5" t="n">
-        <v>38.97125</v>
+        <v>38.82125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.95</v>
       </c>
       <c r="M6" t="n">
-        <v>1.8025</v>
+        <v>1.57875</v>
       </c>
       <c r="N6" t="n">
-        <v>38.39875</v>
+        <v>38.305</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.41</v>
       </c>
       <c r="M7" t="n">
-        <v>1.51875</v>
+        <v>1.36125</v>
       </c>
       <c r="N7" t="n">
-        <v>38.15125</v>
+        <v>37.65875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>1.34375</v>
+        <v>1.23875</v>
       </c>
       <c r="N8" t="n">
-        <v>37.87625</v>
+        <v>37.475</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>1.45375</v>
       </c>
       <c r="N10" t="n">
-        <v>39.43875000000001</v>
+        <v>39.43875</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>1.965</v>
       </c>
       <c r="N12" t="n">
-        <v>41.19499999999999</v>
+        <v>41.195</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>2.05625</v>
       </c>
       <c r="N13" t="n">
-        <v>41.21749999999999</v>
+        <v>41.2175</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1170</v>
+      </c>
+      <c r="D75" t="n">
+        <v>700</v>
+      </c>
+      <c r="E75" t="n">
+        <v>470</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="G75" t="n">
+        <v>159</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.54%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>152</v>
+      </c>
+      <c r="K75" t="n">
+        <v>93</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.015</v>
+      </c>
+      <c r="N75" t="n">
+        <v>42.4575</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.8400000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3076923076923077</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.210000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07403136531365317</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3678929765886289</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.200000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.0290205562273278</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
